--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_005.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_005.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="134">
   <si>
     <t>Sezione</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Firmatario</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto da trascrivere</t>
@@ -466,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.3984375" customWidth="true" bestFit="true"/>
@@ -2826,19 +2832,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2849,16 +2855,16 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>102</v>
@@ -2872,7 +2878,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>103</v>
@@ -2881,7 +2887,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>104</v>
@@ -2895,19 +2901,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -2918,16 +2924,16 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>107</v>
@@ -2941,16 +2947,16 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>109</v>
@@ -2964,7 +2970,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>110</v>
@@ -2973,7 +2979,7 @@
         <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>111</v>
@@ -2987,19 +2993,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="C110" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3010,16 +3016,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>102</v>
@@ -3033,7 +3039,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>103</v>
@@ -3042,7 +3048,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>104</v>
@@ -3056,19 +3062,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3079,7 +3085,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>116</v>
@@ -3088,7 +3094,7 @@
         <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>117</v>
@@ -3102,7 +3108,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>118</v>
@@ -3111,7 +3117,7 @@
         <v>13</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>119</v>
@@ -3125,7 +3131,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>120</v>
@@ -3134,7 +3140,7 @@
         <v>13</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>121</v>
@@ -3148,7 +3154,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>122</v>
@@ -3157,7 +3163,7 @@
         <v>13</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>123</v>
@@ -3171,7 +3177,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>124</v>
@@ -3180,7 +3186,7 @@
         <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>125</v>
@@ -3194,19 +3200,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3217,16 +3223,16 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>131</v>
@@ -3235,6 +3241,29 @@
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>21</v>
       </c>
     </row>
